--- a/artfynd/A 58205-2023 artfynd.xlsx
+++ b/artfynd/A 58205-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58205-2023 artfynd.xlsx
+++ b/artfynd/A 58205-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112605269</v>
+        <v>112610135</v>
       </c>
       <c r="B8" t="n">
-        <v>89791</v>
+        <v>5473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692982</v>
+        <v>692973</v>
       </c>
       <c r="R8" t="n">
-        <v>7184237</v>
+        <v>7184233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112605268</v>
+        <v>112605266</v>
       </c>
       <c r="B9" t="n">
-        <v>5473</v>
+        <v>56730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1496,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692974</v>
+        <v>692921</v>
       </c>
       <c r="R9" t="n">
-        <v>7184230</v>
+        <v>7184257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112610135</v>
+        <v>112610134</v>
       </c>
       <c r="B10" t="n">
-        <v>5473</v>
+        <v>77856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692973</v>
+        <v>692902</v>
       </c>
       <c r="R10" t="n">
-        <v>7184233</v>
+        <v>7184232</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,434 +1695,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112610136</v>
-      </c>
-      <c r="B11" t="n">
-        <v>89791</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Forsholm, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>692983</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7184238</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112605266</v>
-      </c>
-      <c r="B12" t="n">
-        <v>56730</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Forsholm, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>692921</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7184257</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112605267</v>
-      </c>
-      <c r="B13" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Forsholm, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>692901</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7184234</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112610134</v>
-      </c>
-      <c r="B14" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Forsholm, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>692902</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7184232</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
